--- a/artfynd/A 60557-2021 artfynd.xlsx
+++ b/artfynd/A 60557-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 60557-2021 artfynd.xlsx
+++ b/artfynd/A 60557-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1521,10 +1521,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>97398798</v>
+        <v>112044186</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
+        <v>96736</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1554,26 +1554,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hedemora, Dlr</t>
+          <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>554704.7698631033</v>
+        <v>554675</v>
       </c>
       <c r="R9" t="n">
-        <v>6698728.596501934</v>
+        <v>6698785</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1597,22 +1591,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-12-04</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>12:43</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-12-04</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>12:43</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1627,22 +1611,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112044186</v>
+        <v>112044170</v>
       </c>
       <c r="B10" t="n">
-        <v>96736</v>
+        <v>89994</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1655,21 +1639,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1679,10 +1663,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>554675</v>
+        <v>554745</v>
       </c>
       <c r="R10" t="n">
-        <v>6698785</v>
+        <v>6698641</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1741,10 +1725,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112044170</v>
+        <v>112044190</v>
       </c>
       <c r="B11" t="n">
-        <v>89994</v>
+        <v>96736</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1757,21 +1741,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1781,10 +1765,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>554745</v>
+        <v>554682</v>
       </c>
       <c r="R11" t="n">
-        <v>6698641</v>
+        <v>6698694</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1843,7 +1827,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112044190</v>
+        <v>112044189</v>
       </c>
       <c r="B12" t="n">
         <v>96736</v>
@@ -1883,10 +1867,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>554682</v>
+        <v>554686</v>
       </c>
       <c r="R12" t="n">
-        <v>6698694</v>
+        <v>6698721</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1945,7 +1929,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112044189</v>
+        <v>112044194</v>
       </c>
       <c r="B13" t="n">
         <v>96736</v>
@@ -1985,10 +1969,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>554686</v>
+        <v>554746</v>
       </c>
       <c r="R13" t="n">
-        <v>6698721</v>
+        <v>6698619</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2047,7 +2031,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112044194</v>
+        <v>112044185</v>
       </c>
       <c r="B14" t="n">
         <v>96736</v>
@@ -2087,10 +2071,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>554746</v>
+        <v>554752</v>
       </c>
       <c r="R14" t="n">
-        <v>6698619</v>
+        <v>6698637</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2149,7 +2133,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>112044185</v>
+        <v>112044191</v>
       </c>
       <c r="B15" t="n">
         <v>96736</v>
@@ -2189,10 +2173,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>554752</v>
+        <v>554719</v>
       </c>
       <c r="R15" t="n">
-        <v>6698637</v>
+        <v>6698669</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2251,7 +2235,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112044191</v>
+        <v>112044193</v>
       </c>
       <c r="B16" t="n">
         <v>96736</v>
@@ -2291,10 +2275,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>554719</v>
+        <v>554737</v>
       </c>
       <c r="R16" t="n">
-        <v>6698669</v>
+        <v>6698616</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2353,7 +2337,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>112044193</v>
+        <v>112044174</v>
       </c>
       <c r="B17" t="n">
         <v>96736</v>
@@ -2387,16 +2371,24 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>554737</v>
+        <v>554690</v>
       </c>
       <c r="R17" t="n">
-        <v>6698616</v>
+        <v>6698722</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2437,6 +2429,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2455,7 +2448,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>112044174</v>
+        <v>112044192</v>
       </c>
       <c r="B18" t="n">
         <v>96736</v>
@@ -2489,24 +2482,16 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>554690</v>
+        <v>554727</v>
       </c>
       <c r="R18" t="n">
-        <v>6698722</v>
+        <v>6698622</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2547,7 +2532,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2566,10 +2550,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>112044192</v>
+        <v>112044163</v>
       </c>
       <c r="B19" t="n">
-        <v>96736</v>
+        <v>56575</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2578,38 +2562,46 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>554727</v>
+        <v>554650</v>
       </c>
       <c r="R19" t="n">
-        <v>6698622</v>
+        <v>6698762</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2668,10 +2660,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>112044163</v>
+        <v>112044187</v>
       </c>
       <c r="B20" t="n">
-        <v>56575</v>
+        <v>96736</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2680,46 +2672,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>554650</v>
+        <v>554629</v>
       </c>
       <c r="R20" t="n">
-        <v>6698762</v>
+        <v>6698775</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2778,7 +2762,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>112044187</v>
+        <v>112044188</v>
       </c>
       <c r="B21" t="n">
         <v>96736</v>
@@ -2818,10 +2802,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>554629</v>
+        <v>554647</v>
       </c>
       <c r="R21" t="n">
-        <v>6698775</v>
+        <v>6698760</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2880,10 +2864,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>112044188</v>
+        <v>97398439</v>
       </c>
       <c r="B22" t="n">
-        <v>96736</v>
+        <v>96334</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2913,20 +2897,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kyrkberget, Dlr</t>
+          <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>554647</v>
+        <v>554771.9511894669</v>
       </c>
       <c r="R22" t="n">
-        <v>6698760</v>
+        <v>6698637.242191116</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2950,12 +2945,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2021-12-04</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2021-12-04</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2970,22 +2975,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t xml:space="preserve">FREDRIK  Månsson </t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t xml:space="preserve">FREDRIK  Månsson </t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>97398439</v>
+        <v>112044171</v>
       </c>
       <c r="B23" t="n">
-        <v>96334</v>
+        <v>89835</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2994,52 +2999,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hedemora, Dlr</t>
+          <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>554771.9511894669</v>
+        <v>554758</v>
       </c>
       <c r="R23" t="n">
-        <v>6698637.242191116</v>
+        <v>6698625</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3063,22 +3057,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2021-12-04</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>12:09</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2021-12-04</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>12:09</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3093,22 +3077,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t xml:space="preserve">FREDRIK  Månsson </t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>112044171</v>
+        <v>112044162</v>
       </c>
       <c r="B24" t="n">
-        <v>89835</v>
+        <v>56575</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3121,34 +3105,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>554758</v>
+        <v>554765</v>
       </c>
       <c r="R24" t="n">
-        <v>6698625</v>
+        <v>6698666</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3207,10 +3199,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>112044162</v>
+        <v>112044184</v>
       </c>
       <c r="B25" t="n">
-        <v>56575</v>
+        <v>96736</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3219,46 +3211,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kyrkberget, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>554765</v>
+        <v>554833</v>
       </c>
       <c r="R25" t="n">
-        <v>6698666</v>
+        <v>6698646</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3317,7 +3301,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>112044184</v>
+        <v>112044195</v>
       </c>
       <c r="B26" t="n">
         <v>96736</v>
@@ -3357,10 +3341,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>554833</v>
+        <v>554806</v>
       </c>
       <c r="R26" t="n">
-        <v>6698646</v>
+        <v>6698598</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3419,10 +3403,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>112044195</v>
+        <v>112044158</v>
       </c>
       <c r="B27" t="n">
-        <v>96736</v>
+        <v>89554</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3431,25 +3415,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3459,10 +3443,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>554806</v>
+        <v>554756</v>
       </c>
       <c r="R27" t="n">
-        <v>6698598</v>
+        <v>6698631</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3518,108 +3502,6 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>112044158</v>
-      </c>
-      <c r="B28" t="n">
-        <v>89554</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>Kyrkberget, Dlr</t>
-        </is>
-      </c>
-      <c r="Q28" t="n">
-        <v>554756</v>
-      </c>
-      <c r="R28" t="n">
-        <v>6698631</v>
-      </c>
-      <c r="S28" t="n">
-        <v>15</v>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>Hedemora</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>Husby</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>2023-09-12</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>2023-09-12</t>
-        </is>
-      </c>
-      <c r="AD28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT28" t="inlineStr"/>
-      <c r="AW28" t="inlineStr">
-        <is>
-          <t>Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
